--- a/exports/trend_1d/MAZDOCK_full_report.xlsx
+++ b/exports/trend_1d/MAZDOCK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>36.45</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44246</v>
+        <v>44249</v>
       </c>
       <c r="H2" t="n">
-        <v>109.15</v>
+        <v>104.05</v>
       </c>
       <c r="I2" t="n">
         <v>104.0854177247883</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K2" t="n">
-        <v>19.81</v>
+        <v>14.22</v>
       </c>
       <c r="L2" t="n">
         <v>9.44</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.32</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44334</v>
+        <v>44335</v>
       </c>
       <c r="H3" t="n">
-        <v>102.9</v>
+        <v>108.65</v>
       </c>
       <c r="I3" t="n">
         <v>106.7364696380351</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" t="n">
-        <v>1.11</v>
+        <v>-4.42</v>
       </c>
       <c r="L3" t="n">
         <v>16</v>
@@ -612,7 +647,7 @@
         <v>2.14</v>
       </c>
       <c r="N3" t="n">
-        <v>4.17</v>
+        <v>5.59</v>
       </c>
       <c r="O3" t="n">
         <v>-4.67</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.92</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44425</v>
+        <v>44426</v>
       </c>
       <c r="H4" t="n">
-        <v>118.4</v>
+        <v>117.9</v>
       </c>
       <c r="I4" t="n">
         <v>118.2492667367183</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K4" t="n">
-        <v>8.970000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="L4" t="n">
         <v>5.2</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>11.94</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44454</v>
+        <v>44455</v>
       </c>
       <c r="H5" t="n">
-        <v>125.2</v>
+        <v>128.6</v>
       </c>
       <c r="I5" t="n">
         <v>128.0486731795664</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.19</v>
+        <v>-9.08</v>
       </c>
       <c r="L5" t="n">
-        <v>11.28</v>
+        <v>11.54</v>
       </c>
       <c r="M5" t="n">
         <v>1.49</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.49</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H6" t="n">
-        <v>144.7</v>
+        <v>136.2</v>
       </c>
       <c r="I6" t="n">
         <v>136.5351023467933</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K6" t="n">
-        <v>12.52</v>
+        <v>5.91</v>
       </c>
       <c r="L6" t="n">
         <v>3.46</v>
@@ -783,7 +854,7 @@
         <v>1.75</v>
       </c>
       <c r="N6" t="n">
-        <v>4.37</v>
+        <v>5.87</v>
       </c>
       <c r="O6" t="n">
         <v>2.72</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>18.29</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44560</v>
+        <v>44561</v>
       </c>
       <c r="H7" t="n">
-        <v>137.85</v>
+        <v>139.4</v>
       </c>
       <c r="I7" t="n">
         <v>139.2819723426168</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.21</v>
+        <v>-2.35</v>
       </c>
       <c r="L7" t="n">
         <v>7.86</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H8" t="n">
-        <v>137</v>
+        <v>128.7</v>
       </c>
       <c r="I8" t="n">
         <v>133.8722315424687</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.72</v>
+        <v>-7.68</v>
       </c>
       <c r="L8" t="n">
-        <v>3.37</v>
+        <v>9.25</v>
       </c>
       <c r="M8" t="n">
         <v>3.06</v>
       </c>
       <c r="N8" t="n">
-        <v>4.05</v>
+        <v>6.06</v>
       </c>
       <c r="O8" t="n">
         <v>1.12</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>13.4</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H9" t="n">
-        <v>125.7</v>
+        <v>135.8</v>
       </c>
       <c r="I9" t="n">
         <v>128.9752656149846</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K9" t="n">
-        <v>2.33</v>
+        <v>-5.52</v>
       </c>
       <c r="L9" t="n">
-        <v>8.16</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>3.22</v>
       </c>
       <c r="N9" t="n">
-        <v>6.97</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="O9" t="n">
         <v>-6.06</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>13.04</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44690</v>
+        <v>44691</v>
       </c>
       <c r="H10" t="n">
-        <v>140.9</v>
+        <v>137.7</v>
       </c>
       <c r="I10" t="n">
         <v>139.7991379754902</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K10" t="n">
-        <v>3.76</v>
+        <v>1.4</v>
       </c>
       <c r="L10" t="n">
         <v>6.89</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>17.07</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44763</v>
+        <v>44764</v>
       </c>
       <c r="H11" t="n">
-        <v>135.6</v>
+        <v>137.5</v>
       </c>
       <c r="I11" t="n">
         <v>136.1037863458246</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K11" t="n">
-        <v>1.53</v>
+        <v>0.15</v>
       </c>
       <c r="L11" t="n">
         <v>11.66</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.74</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H12" t="n">
-        <v>421.7</v>
+        <v>395.75</v>
       </c>
       <c r="I12" t="n">
         <v>398.3285493776692</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K12" t="n">
-        <v>206.69</v>
+        <v>187.82</v>
       </c>
       <c r="L12" t="n">
         <v>2.62</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>20.06</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45027</v>
+        <v>45028</v>
       </c>
       <c r="H13" t="n">
-        <v>345.8</v>
+        <v>355.2</v>
       </c>
       <c r="I13" t="n">
         <v>349.993884673889</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K13" t="n">
-        <v>12.62</v>
+        <v>10.25</v>
       </c>
       <c r="L13" t="n">
         <v>7.53</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.14</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H14" t="n">
-        <v>1037.9</v>
+        <v>967.8</v>
       </c>
       <c r="I14" t="n">
         <v>997.0136279636405</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K14" t="n">
-        <v>192.2</v>
+        <v>172.47</v>
       </c>
       <c r="L14" t="n">
         <v>2.96</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>16.34</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45278</v>
+        <v>45279</v>
       </c>
       <c r="H15" t="n">
-        <v>1063.4</v>
+        <v>1070</v>
       </c>
       <c r="I15" t="n">
         <v>1067.961369455572</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.880000000000001</v>
+        <v>-10.56</v>
       </c>
       <c r="L15" t="n">
-        <v>12.37</v>
+        <v>14.43</v>
       </c>
       <c r="M15" t="n">
         <v>4.33</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.41</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45324</v>
+        <v>45327</v>
       </c>
       <c r="H16" t="n">
-        <v>1102.85</v>
+        <v>1048.9</v>
       </c>
       <c r="I16" t="n">
         <v>1059.215813084952</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K16" t="n">
-        <v>3.07</v>
+        <v>-1.97</v>
       </c>
       <c r="L16" t="n">
         <v>5.5</v>
@@ -1353,7 +1544,7 @@
         <v>-0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.38</v>
+        <v>4.89</v>
       </c>
       <c r="O16" t="n">
         <v>0.62</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>15.79</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H17" t="n">
-        <v>997.8</v>
+        <v>1118.35</v>
       </c>
       <c r="I17" t="n">
         <v>1047.941415277597</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K17" t="n">
-        <v>4.87</v>
+        <v>-6.62</v>
       </c>
       <c r="L17" t="n">
         <v>7.73</v>
@@ -1410,7 +1613,7 @@
         <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>7.33</v>
+        <v>12.08</v>
       </c>
       <c r="O17" t="n">
         <v>-4.89</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>18.21</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H18" t="n">
-        <v>1628.8</v>
+        <v>1339.75</v>
       </c>
       <c r="I18" t="n">
         <v>1379.066060977321</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K18" t="n">
-        <v>45.64</v>
+        <v>19.8</v>
       </c>
       <c r="L18" t="n">
         <v>10.98</v>
@@ -1467,7 +1682,7 @@
         <v>2.21</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>17.75</v>
       </c>
       <c r="O18" t="n">
         <v>12.08</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>36.86</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H19" t="n">
-        <v>1694.95</v>
+        <v>1938.8</v>
       </c>
       <c r="I19" t="n">
         <v>1758.465132392779</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>-26.51</v>
+        <v>-44.71</v>
       </c>
       <c r="L19" t="n">
-        <v>27.26</v>
+        <v>48.91</v>
       </c>
       <c r="M19" t="n">
         <v>1.43</v>
       </c>
       <c r="N19" t="n">
-        <v>12.95</v>
+        <v>14.39</v>
       </c>
       <c r="O19" t="n">
         <v>-17.75</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>26.15</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45523</v>
+        <v>45524</v>
       </c>
       <c r="H20" t="n">
-        <v>2362.4</v>
+        <v>2149.8</v>
       </c>
       <c r="I20" t="n">
         <v>2286.4065858801</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K20" t="n">
-        <v>21.85</v>
+        <v>10.88</v>
       </c>
       <c r="L20" t="n">
         <v>13.48</v>
@@ -1581,7 +1820,7 @@
         <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>5.81</v>
+        <v>9</v>
       </c>
       <c r="O20" t="n">
         <v>14.39</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>25.07</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45582</v>
+        <v>45583</v>
       </c>
       <c r="H21" t="n">
-        <v>2118.9</v>
+        <v>2263.2</v>
       </c>
       <c r="I21" t="n">
         <v>2239.843108874248</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K21" t="n">
-        <v>1.44</v>
+        <v>-5.27</v>
       </c>
       <c r="L21" t="n">
         <v>14.55</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>15.43</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45590</v>
+        <v>45593</v>
       </c>
       <c r="H22" t="n">
-        <v>2031.15</v>
+        <v>2008</v>
       </c>
       <c r="I22" t="n">
         <v>2026.384210547203</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.25</v>
+        <v>-11.28</v>
       </c>
       <c r="L22" t="n">
-        <v>11.52</v>
+        <v>11.81</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>19.26</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H23" t="n">
-        <v>2117.1</v>
+        <v>2234.8</v>
       </c>
       <c r="I23" t="n">
         <v>2213.289162313419</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.43</v>
+        <v>-11.29</v>
       </c>
       <c r="L23" t="n">
-        <v>10.7</v>
+        <v>12.05</v>
       </c>
       <c r="M23" t="n">
         <v>4.84</v>
       </c>
       <c r="N23" t="n">
-        <v>4.59</v>
+        <v>5.56</v>
       </c>
       <c r="O23" t="n">
         <v>-1.14</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.35</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="H24" t="n">
-        <v>2317.4</v>
+        <v>2269.05</v>
       </c>
       <c r="I24" t="n">
         <v>2301.531936556369</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7</v>
+        <v>1.53</v>
       </c>
       <c r="L24" t="n">
         <v>5.04</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>14.46</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45674</v>
+        <v>45677</v>
       </c>
       <c r="H25" t="n">
-        <v>2315.05</v>
+        <v>2438.45</v>
       </c>
       <c r="I25" t="n">
         <v>2437.457198747934</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.03</v>
+        <v>-7.47</v>
       </c>
       <c r="L25" t="n">
-        <v>4.45</v>
+        <v>10.02</v>
       </c>
       <c r="M25" t="n">
         <v>2.25</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>16.5</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="H26" t="n">
-        <v>2083.1</v>
+        <v>1961.75</v>
       </c>
       <c r="I26" t="n">
         <v>2037.830821815199</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K26" t="n">
-        <v>-14.57</v>
+        <v>-19.55</v>
       </c>
       <c r="L26" t="n">
-        <v>15.31</v>
+        <v>20.3</v>
       </c>
       <c r="M26" t="n">
         <v>2.09</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>23.27</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H27" t="n">
-        <v>2376.5</v>
+        <v>2625.25</v>
       </c>
       <c r="I27" t="n">
         <v>2418.314433525513</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K27" t="n">
-        <v>-21.14</v>
+        <v>-33.82</v>
       </c>
       <c r="L27" t="n">
-        <v>21.76</v>
+        <v>34.98</v>
       </c>
       <c r="M27" t="n">
         <v>1.26</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>17.43</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H28" t="n">
-        <v>2542.2</v>
+        <v>2317.3</v>
       </c>
       <c r="I28" t="n">
         <v>2345.694226586241</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.16</v>
+        <v>-11.73</v>
       </c>
       <c r="L28" t="n">
-        <v>9.529999999999999</v>
+        <v>16.2</v>
       </c>
       <c r="M28" t="n">
-        <v>5.94</v>
+        <v>12.63</v>
       </c>
       <c r="N28" t="n">
-        <v>7.14</v>
+        <v>8.85</v>
       </c>
       <c r="O28" t="n">
         <v>10.47</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>18.21</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H29" t="n">
-        <v>2710.6</v>
+        <v>2764.6</v>
       </c>
       <c r="I29" t="n">
         <v>2739.259652643091</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>-16.97</v>
+        <v>-19.3</v>
       </c>
       <c r="L29" t="n">
         <v>21.47</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>15.63</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45819</v>
+        <v>45820</v>
       </c>
       <c r="H30" t="n">
-        <v>3314.6</v>
+        <v>3210.4</v>
       </c>
       <c r="I30" t="n">
         <v>3248.122996961722</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K30" t="n">
-        <v>19.89</v>
+        <v>16.13</v>
       </c>
       <c r="L30" t="n">
         <v>6.5</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>14.45</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="H31" t="n">
-        <v>2794.5</v>
+        <v>2924.7</v>
       </c>
       <c r="I31" t="n">
         <v>2871.324616692332</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K31" t="n">
-        <v>12.95</v>
+        <v>8.9</v>
       </c>
       <c r="L31" t="n">
         <v>4.94</v>
@@ -2208,7 +2579,7 @@
         <v>3.65</v>
       </c>
       <c r="N31" t="n">
-        <v>4.43</v>
+        <v>4.66</v>
       </c>
       <c r="O31" t="n">
         <v>-3.14</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>10.11</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="H32" t="n">
-        <v>2827.6</v>
+        <v>2751.1</v>
       </c>
       <c r="I32" t="n">
         <v>2795.510301094029</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.32</v>
+        <v>-5.94</v>
       </c>
       <c r="L32" t="n">
-        <v>4.53</v>
+        <v>6.83</v>
       </c>
       <c r="M32" t="n">
         <v>0.22</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>10.63</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="H33" t="n">
-        <v>2408.2</v>
+        <v>2544.8</v>
       </c>
       <c r="I33" t="n">
         <v>2544.321021001612</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K33" t="n">
-        <v>12.46</v>
+        <v>7.5</v>
       </c>
       <c r="L33" t="n">
         <v>6.49</v>
@@ -2322,7 +2717,7 @@
         <v>2.12</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>5.67</v>
       </c>
       <c r="O33" t="n">
         <v>-2.71</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>11.16</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H34" t="n">
-        <v>2436.7</v>
+        <v>2332.3</v>
       </c>
       <c r="I34" t="n">
         <v>2358.935270808758</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.25</v>
+        <v>-8.35</v>
       </c>
       <c r="L34" t="n">
-        <v>5.65</v>
+        <v>9.01</v>
       </c>
       <c r="M34" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>2.95</v>
+        <v>4.28</v>
       </c>
       <c r="O34" t="n">
         <v>5.67</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>12.18</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="H35" t="n">
-        <v>2517.2</v>
+        <v>2572.9</v>
       </c>
       <c r="I35" t="n">
         <v>2537.951825651888</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.93</v>
+        <v>-10.32</v>
       </c>
       <c r="L35" t="n">
-        <v>8.77</v>
+        <v>10.88</v>
       </c>
       <c r="M35" t="n">
         <v>1.03</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>11.43</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="H36" t="n">
-        <v>2280.8</v>
+        <v>2256.4</v>
       </c>
       <c r="I36" t="n">
         <v>2278.693269099774</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K36" t="n">
-        <v>-11.35</v>
+        <v>-12.3</v>
       </c>
       <c r="L36" t="n">
-        <v>11.73</v>
+        <v>13.09</v>
       </c>
       <c r="M36" t="n">
         <v>0.62</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>10.42</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="H37" t="n">
-        <v>2352.5</v>
+        <v>2471.9</v>
       </c>
       <c r="I37" t="n">
         <v>2405.388815784146</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.26</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>7.02</v>
+        <v>13.46</v>
       </c>
       <c r="M37" t="n">
-        <v>0.67</v>
+        <v>1.31</v>
       </c>
       <c r="N37" t="n">
         <v>8.640000000000001</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>12.7</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="H38" t="n">
-        <v>2162.9</v>
+        <v>2065.2</v>
       </c>
       <c r="I38" t="n">
         <v>2157.892059214842</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>-12.5</v>
+        <v>-16.45</v>
       </c>
       <c r="L38" t="n">
-        <v>12.78</v>
+        <v>16.77</v>
       </c>
       <c r="M38" t="n">
         <v>1.48</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>17.38</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="H39" t="n">
-        <v>2395</v>
+        <v>2435.5</v>
       </c>
       <c r="I39" t="n">
         <v>2424.096562394684</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K39" t="n">
-        <v>-15.97</v>
+        <v>-17.93</v>
       </c>
       <c r="L39" t="n">
-        <v>19.36</v>
+        <v>19.53</v>
       </c>
       <c r="M39" t="n">
         <v>5.7</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>14.42</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H40" t="n">
-        <v>2565.8</v>
+        <v>2443.8</v>
       </c>
       <c r="I40" t="n">
         <v>2501.983946963135</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K40" t="n">
-        <v>5.35</v>
+        <v>0.34</v>
       </c>
       <c r="L40" t="n">
         <v>2.57</v>
@@ -2721,7 +3200,7 @@
         <v>1.83</v>
       </c>
       <c r="N40" t="n">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="O40" t="n">
         <v>1.69</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>13.31</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H41" t="n">
-        <v>2467.4</v>
+        <v>2552.4</v>
       </c>
       <c r="I41" t="n">
         <v>2550.883140483193</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.97</v>
+        <v>-4.44</v>
       </c>
       <c r="L41" t="n">
         <v>5.1</v>
@@ -2778,7 +3269,7 @@
         <v>1.38</v>
       </c>
       <c r="N41" t="n">
-        <v>3.06</v>
+        <v>3.44</v>
       </c>
       <c r="O41" t="n">
         <v>-4.75</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>9.31</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="H42" t="n">
-        <v>2402.6</v>
+        <v>2359.9</v>
       </c>
       <c r="I42" t="n">
         <v>2370.644530937999</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.87</v>
+        <v>-7.54</v>
       </c>
       <c r="L42" t="n">
-        <v>7.15</v>
+        <v>7.89</v>
       </c>
       <c r="M42" t="n">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="N42" t="n">
         <v>3.18</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.34</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="H43" t="n">
-        <v>2380.5</v>
+        <v>2530</v>
       </c>
       <c r="I43" t="n">
         <v>2440.073745413827</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.87</v>
+        <v>-7.21</v>
       </c>
       <c r="L43" t="n">
-        <v>2.72</v>
+        <v>9.07</v>
       </c>
       <c r="M43" t="n">
         <v>1.12</v>
       </c>
       <c r="N43" t="n">
-        <v>2.7</v>
+        <v>6.28</v>
       </c>
       <c r="O43" t="n">
         <v>-1.78</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.81</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="H44" t="n">
-        <v>2466.4</v>
+        <v>2408.8</v>
       </c>
       <c r="I44" t="n">
         <v>2425.260241597279</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.51</v>
+        <v>-4.79</v>
       </c>
       <c r="L44" t="n">
         <v>6.19</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -3009,6 +3548,14 @@
       <c r="Q45" t="n">
         <v>33</v>
       </c>
+      <c r="R45" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5829,7 +6376,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.4</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="6">
@@ -5839,7 +6386,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -5849,7 +6396,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8">
@@ -5859,7 +6406,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -5869,7 +6416,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64.5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -5879,7 +6426,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90.8</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="11">
@@ -5889,7 +6436,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +6446,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -5909,7 +6456,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46.5</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="14">
@@ -5919,7 +6466,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.390000000000001</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="15">
@@ -5929,7 +6476,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21.54</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="16">
@@ -5939,7 +6486,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-3.34</v>
+        <v>-8.720000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -5949,7 +6496,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>206.69</v>
+        <v>187.82</v>
       </c>
     </row>
     <row r="18">
@@ -5959,7 +6506,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.5</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="19">
@@ -5969,7 +6516,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.289999999999999</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="20">
@@ -5979,7 +6526,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.73</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="21">
@@ -5989,7 +6536,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>27.26</v>
+        <v>48.91</v>
       </c>
     </row>
     <row r="22">
@@ -5999,7 +6546,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -6009,7 +6556,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -6019,7 +6566,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="25">
@@ -6029,7 +6576,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.5</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="26">
@@ -6039,7 +6586,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.52</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="27">
@@ -6049,7 +6596,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14.82</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="28">
@@ -6059,7 +6606,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
